--- a/Trade_Lifecycle_Tracker_Enhanced.xlsx
+++ b/Trade_Lifecycle_Tracker_Enhanced.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="363">
   <si>
     <t xml:space="preserve">TRADE LIFECYCLE TRACKER — IronHub Capital Operations</t>
   </si>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">BUY</t>
   </si>
   <si>
-    <t xml:space="preserve">Motilal Oswal</t>
+    <t xml:space="preserve">ICICI Securities</t>
   </si>
   <si>
     <t xml:space="preserve">HDFC Custody</t>
@@ -150,6 +150,9 @@
     <t xml:space="preserve">S-7 Settlement</t>
   </si>
   <si>
+    <t xml:space="preserve">Completed – Settled</t>
+  </si>
+  <si>
     <t xml:space="preserve">TRD-002</t>
   </si>
   <si>
@@ -177,6 +180,9 @@
     <t xml:space="preserve">S-5 Matching</t>
   </si>
   <si>
+    <t xml:space="preserve">Break – Investigation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Price mismatch: Our ₹1520.50 vs CP ₹1518.00 — Break raised on Omegeo CTM</t>
   </si>
   <si>
@@ -330,9 +336,6 @@
     <t xml:space="preserve">IN0020210203</t>
   </si>
   <si>
-    <t xml:space="preserve">ICICI Securities</t>
-  </si>
-  <si>
     <t xml:space="preserve">Deutsche Custody</t>
   </si>
   <si>
@@ -351,7 +354,7 @@
     <t xml:space="preserve">S-6 Clearing</t>
   </si>
   <si>
-    <t xml:space="preserve">SWIFT MT541 dispatched; margin blocked at CCIL; awaiting CCP confirmation</t>
+    <t xml:space="preserve">In Progress</t>
   </si>
   <si>
     <t xml:space="preserve">TRD-009</t>
@@ -378,9 +381,6 @@
     <t xml:space="preserve">S-4 Allocation</t>
   </si>
   <si>
-    <t xml:space="preserve">Allocation to fund IM-3 completed; awaiting broker affirmation</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRD-010</t>
   </si>
   <si>
@@ -408,9 +408,6 @@
     <t xml:space="preserve">14:10:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Settled T+1; accrued interest ₹4,823 calculated and booked</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRD-011</t>
   </si>
   <si>
@@ -429,7 +426,7 @@
     <t xml:space="preserve">10:40:00</t>
   </si>
   <si>
-    <t xml:space="preserve">MT543 sent; custodian acknowledged; net DVP obligation ₹30,36,000</t>
+    <t xml:space="preserve">Ready for Settlement</t>
   </si>
   <si>
     <t xml:space="preserve">TRD-012</t>
@@ -465,9 +462,6 @@
     <t xml:space="preserve">12:30:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Margin ₹2.2L posted; cleared NSCCL; MTM updated; daily settlement complete</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRD-013</t>
   </si>
   <si>
@@ -486,9 +480,6 @@
     <t xml:space="preserve">12:45:00</t>
   </si>
   <si>
-    <t xml:space="preserve">FX futures cleared via CCIL; daily MTM ₹-12,400; position live</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRD-014</t>
   </si>
   <si>
@@ -507,9 +498,6 @@
     <t xml:space="preserve">14:00:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Option premium settled; position in OMS marked active</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRD-015</t>
   </si>
   <si>
@@ -561,9 +549,6 @@
     <t xml:space="preserve">Pending Match</t>
   </si>
   <si>
-    <t xml:space="preserve">In Progress</t>
-  </si>
-  <si>
     <t xml:space="preserve">Category</t>
   </si>
   <si>
@@ -576,9 +561,6 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">100.0%</t>
-  </si>
-  <si>
     <t xml:space="preserve">SETTLEMENT STATUS BREAKDOWN</t>
   </si>
   <si>
@@ -591,22 +573,13 @@
     <t xml:space="preserve">Risk Flag</t>
   </si>
   <si>
-    <t xml:space="preserve">Completed – Settled</t>
-  </si>
-  <si>
     <t xml:space="preserve">✔ Clean</t>
   </si>
   <si>
     <t xml:space="preserve">⚠ Monitor</t>
   </si>
   <si>
-    <t xml:space="preserve">Break – Investigation</t>
-  </si>
-  <si>
     <t xml:space="preserve">✖ Urgent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ready for Settlement</t>
   </si>
   <si>
     <t xml:space="preserve">→ STP</t>
@@ -1184,7 +1157,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="0.0\%"/>
+    <numFmt numFmtId="167" formatCode="\₹#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="30">
@@ -1578,7 +1551,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1723,7 +1696,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1747,15 +1720,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1763,7 +1732,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1775,15 +1752,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2128,23 +2097,23 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="16" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="9.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="13.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="13.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="16" style="0" width="13.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="20.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="48.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2355,15 +2324,14 @@
       <c r="T5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U5" s="10" t="str">
-        <f aca="false">IF(V5&lt;&gt;"","Break – Investigation",IF(T5="S-7 Settlement","Completed – Settled",IF(T5="S-6 Clearing","Ready for Settlement",IF(T5="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Completed – Settled</v>
+      <c r="U5" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="V5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>26</v>
@@ -2372,13 +2340,13 @@
         <v>27</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>300</v>
@@ -2397,10 +2365,10 @@
         <v>456150</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N6" s="12" t="s">
         <v>33</v>
@@ -2409,27 +2377,26 @@
         <v>34</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
       <c r="T6" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="U6" s="17" t="str">
-        <f aca="false">IF(V6&lt;&gt;"","Break – Investigation",IF(T6="S-7 Settlement","Completed – Settled",IF(T6="S-6 Clearing","Ready for Settlement",IF(T6="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
+        <v>49</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="V6" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>26</v>
@@ -2438,10 +2405,10 @@
         <v>27</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>30</v>
@@ -2463,10 +2430,10 @@
         <v>190100</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>33</v>
@@ -2475,27 +2442,26 @@
         <v>34</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R7" s="19"/>
       <c r="S7" s="19"/>
       <c r="T7" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="U7" s="10" t="str">
-        <f aca="false">IF(V7&lt;&gt;"","Break – Investigation",IF(T7="S-7 Settlement","Completed – Settled",IF(T7="S-6 Clearing","Ready for Settlement",IF(T7="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
+        <v>49</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="V7" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>26</v>
@@ -2504,13 +2470,13 @@
         <v>27</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>120</v>
@@ -2529,10 +2495,10 @@
         <v>346800</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N8" s="12" t="s">
         <v>33</v>
@@ -2541,39 +2507,38 @@
         <v>34</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R8" s="15"/>
       <c r="S8" s="15"/>
       <c r="T8" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="U8" s="17" t="str">
-        <f aca="false">IF(V8&lt;&gt;"","Break – Investigation",IF(T8="S-7 Settlement","Completed – Settled",IF(T8="S-6 Clearing","Ready for Settlement",IF(T8="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
+        <v>67</v>
+      </c>
+      <c r="U8" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="V8" s="18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>30</v>
@@ -2595,10 +2560,10 @@
         <v>335000</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>33</v>
@@ -2607,39 +2572,38 @@
         <v>26</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R9" s="19"/>
       <c r="S9" s="19"/>
       <c r="T9" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="U9" s="10" t="str">
-        <f aca="false">IF(V9&lt;&gt;"","Break – Investigation",IF(T9="S-7 Settlement","Completed – Settled",IF(T9="S-6 Clearing","Ready for Settlement",IF(T9="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
+        <v>77</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="V9" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>30</v>
@@ -2661,53 +2625,52 @@
         <v>588000</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N10" s="12" t="s">
         <v>33</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S10" s="15"/>
       <c r="T10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U10" s="17" t="str">
-        <f aca="false">IF(V10&lt;&gt;"","Break – Investigation",IF(T10="S-7 Settlement","Completed – Settled",IF(T10="S-6 Clearing","Ready for Settlement",IF(T10="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
+      <c r="U10" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="V10" s="18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>30</v>
@@ -2729,53 +2692,52 @@
         <v>427500</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>33</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S11" s="19"/>
       <c r="T11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U11" s="10" t="str">
-        <f aca="false">IF(V11&lt;&gt;"","Break – Investigation",IF(T11="S-7 Settlement","Completed – Settled",IF(T11="S-6 Clearing","Ready for Settlement",IF(T11="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
+      <c r="U11" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="V11" s="18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>30</v>
@@ -2797,56 +2759,53 @@
         <v>1025000</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O12" s="12" t="s">
         <v>34</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S12" s="15"/>
       <c r="T12" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="U12" s="17" t="str">
-        <f aca="false">IF(V12&lt;&gt;"","Break – Investigation",IF(T12="S-7 Settlement","Completed – Settled",IF(T12="S-6 Clearing","Ready for Settlement",IF(T12="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
-      </c>
-      <c r="V12" s="18" t="s">
         <v>107</v>
       </c>
+      <c r="U12" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="V12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>50</v>
@@ -2865,35 +2824,32 @@
         <v>4975000</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>34</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R13" s="19"/>
       <c r="S13" s="19"/>
       <c r="T13" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="U13" s="10" t="str">
-        <f aca="false">IF(V13&lt;&gt;"","Break – Investigation",IF(T13="S-7 Settlement","Completed – Settled",IF(T13="S-6 Clearing","Ready for Settlement",IF(T13="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
-      </c>
-      <c r="V13" s="18" t="s">
         <v>116</v>
       </c>
+      <c r="U13" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="V13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
@@ -2903,7 +2859,7 @@
         <v>118</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>119</v>
@@ -2934,13 +2890,13 @@
         <v>121</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>122</v>
@@ -2957,32 +2913,29 @@
       <c r="T14" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U14" s="17" t="str">
-        <f aca="false">IF(V14&lt;&gt;"","Break – Investigation",IF(T14="S-7 Settlement","Completed – Settled",IF(T14="S-6 Clearing","Ready for Settlement",IF(T14="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
-      </c>
-      <c r="V14" s="18" t="s">
-        <v>126</v>
-      </c>
+      <c r="U14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="V14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="F15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>30</v>
@@ -3001,56 +2954,53 @@
         <v>3036000</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>34</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q15" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="S15" s="19"/>
       <c r="T15" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="U15" s="10" t="str">
-        <f aca="false">IF(V15&lt;&gt;"","Break – Investigation",IF(T15="S-7 Settlement","Completed – Settled",IF(T15="S-6 Clearing","Ready for Settlement",IF(T15="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
-      </c>
-      <c r="V15" s="18" t="s">
-        <v>133</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="U15" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="V15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="E16" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="F16" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>50</v>
@@ -3069,55 +3019,52 @@
         <v>1107500</v>
       </c>
       <c r="L16" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="M16" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="M16" s="13" t="s">
+      <c r="N16" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>140</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>26</v>
       </c>
       <c r="P16" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="R16" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="R16" s="8" t="s">
+      <c r="S16" s="8" t="s">
         <v>143</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>144</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U16" s="17" t="str">
-        <f aca="false">IF(V16&lt;&gt;"","Break – Investigation",IF(T16="S-7 Settlement","Completed – Settled",IF(T16="S-6 Clearing","Ready for Settlement",IF(T16="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
-      </c>
-      <c r="V16" s="18" t="s">
-        <v>145</v>
-      </c>
+      <c r="U16" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="V16" s="18"/>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>30</v>
@@ -3142,52 +3089,49 @@
         <v>31</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>26</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q17" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="S17" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="R17" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>151</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U17" s="10" t="str">
-        <f aca="false">IF(V17&lt;&gt;"","Break – Investigation",IF(T17="S-7 Settlement","Completed – Settled",IF(T17="S-6 Clearing","Ready for Settlement",IF(T17="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
-      </c>
-      <c r="V17" s="18" t="s">
-        <v>152</v>
-      </c>
+      <c r="U17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="V17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>30</v>
@@ -3209,58 +3153,55 @@
         <v>1850</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M18" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="N18" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="N18" s="12" t="s">
-        <v>140</v>
-      </c>
       <c r="O18" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P18" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S18" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>158</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U18" s="17" t="str">
-        <f aca="false">IF(V18&lt;&gt;"","Break – Investigation",IF(T18="S-7 Settlement","Completed – Settled",IF(T18="S-6 Clearing","Ready for Settlement",IF(T18="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
-      </c>
-      <c r="V18" s="18" t="s">
-        <v>159</v>
-      </c>
+      <c r="U18" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="V18" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>80</v>
@@ -3279,10 +3220,10 @@
         <v>987200</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>33</v>
@@ -3291,29 +3232,28 @@
         <v>26</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="S19" s="19"/>
       <c r="T19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="U19" s="10" t="str">
-        <f aca="false">IF(V19&lt;&gt;"","Break – Investigation",IF(T19="S-7 Settlement","Completed – Settled",IF(T19="S-6 Clearing","Ready for Settlement",IF(T19="S-5 Matching","Pending Match","In Progress"))))</f>
-        <v>Break – Investigation</v>
+        <v>49</v>
+      </c>
+      <c r="U19" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="V19" s="18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B20" s="24"/>
       <c r="C20" s="24"/>
@@ -3369,20 +3309,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="7" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="7" style="0" width="2.96"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3400,7 +3340,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -3418,22 +3358,22 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="J4" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>176</v>
-      </c>
       <c r="L4" s="34" t="s">
-        <v>177</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3447,11 +3387,11 @@
       </c>
       <c r="F5" s="37" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"Completed – Settled")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5" s="38" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"Break – Investigation")</f>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J5" s="39" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"Pending Match")</f>
@@ -3459,22 +3399,22 @@
       </c>
       <c r="L5" s="40" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"In Progress")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="41" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D8" s="41" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3490,13 +3430,13 @@
         <v>4755750</v>
       </c>
       <c r="E9" s="43" t="n">
-        <f aca="false">C9/B5*100</f>
-        <v>53.3333333333333</v>
+        <f aca="false">C9/$C$12</f>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C10" s="12" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!C5:C19,"Fixed Income")</f>
@@ -3507,13 +3447,13 @@
         <v>11542250</v>
       </c>
       <c r="E10" s="45" t="n">
-        <f aca="false">C10/B5*100</f>
-        <v>26.6666666666667</v>
+        <f aca="false">C10/$C$12</f>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!C5:C19,"Derivatives")</f>
@@ -3524,13 +3464,13 @@
         <v>1126034</v>
       </c>
       <c r="E11" s="43" t="n">
-        <f aca="false">C11/B5*100</f>
-        <v>20</v>
+        <f aca="false">C11/$C$12</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="25" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C12" s="25" t="n">
         <f aca="false">SUM(C9:C11)</f>
@@ -3540,110 +3480,111 @@
         <f aca="false">SUM(D9:D11)</f>
         <v>17424034</v>
       </c>
-      <c r="E12" s="25" t="s">
-        <v>182</v>
+      <c r="E12" s="47" t="n">
+        <f aca="false">SUM(E9:E11)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
+      <c r="B14" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="C15" s="48" t="s">
+      <c r="B15" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>185</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>186</v>
+      <c r="E15" s="49" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>187</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"Completed – Settled")</f>
-        <v>1</v>
-      </c>
-      <c r="D16" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="43" t="n">
         <f aca="false">C16/B5</f>
-        <v>0.0666666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>177</v>
+        <v>108</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"In Progress")</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="45" t="n">
         <f aca="false">C17/B5</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="52" t="s">
-        <v>189</v>
+        <v>0.133333333333333</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"Break – Investigation")</f>
-        <v>14</v>
-      </c>
-      <c r="D18" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="43" t="n">
         <f aca="false">C18/B5</f>
-        <v>0.933333333333333</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>191</v>
+        <v>0.466666666666667</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"Ready for Settlement")</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="45" t="n">
         <f aca="false">C19/B5</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="54" t="s">
-        <v>193</v>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C20" s="5" t="n">
         <f aca="false">COUNTIF('Trade Lifecycle Tracker'!U5:U19,"Pending Match")</f>
         <v>0</v>
       </c>
-      <c r="D20" s="49" t="n">
+      <c r="D20" s="43" t="n">
         <f aca="false">C20/B5</f>
         <v>0</v>
       </c>
-      <c r="E20" s="55" t="s">
-        <v>194</v>
+      <c r="E20" s="54" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3668,204 +3609,204 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="37.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="27.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="56" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
+      <c r="A1" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="E3" s="57" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="F3" s="58" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="41" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="B4" s="60" t="s">
         <v>200</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="C4" s="60" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="57" t="s">
+      <c r="D4" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="E4" s="60" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="F4" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="D3" s="58" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="B5" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="C5" s="57" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="60" t="s">
+      <c r="D5" s="57" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="E5" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="F5" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="D4" s="61" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="63" t="s">
         <v>211</v>
       </c>
-      <c r="E4" s="61" t="s">
+      <c r="B6" s="60" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="C6" s="60" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="63" t="s">
+      <c r="D6" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="E6" s="60" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="F6" s="61" t="s">
         <v>216</v>
       </c>
-      <c r="D5" s="58" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="B7" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="C7" s="57" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="64" t="s">
+      <c r="D7" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="E7" s="57" t="s">
         <v>221</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="F7" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="61" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="B8" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="C8" s="60" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="65" t="s">
+      <c r="D8" s="60" t="s">
         <v>226</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="E8" s="60" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="F8" s="61" t="s">
         <v>228</v>
       </c>
-      <c r="D7" s="58" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="66" t="s">
         <v>229</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="B9" s="57" t="s">
         <v>230</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="C9" s="57" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="66" t="s">
+      <c r="D9" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="E9" s="57" t="s">
         <v>233</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="F9" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="D8" s="61" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="E8" s="61" t="s">
+      <c r="B10" s="60" t="s">
         <v>236</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="C10" s="60" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="67" t="s">
+      <c r="D10" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="E10" s="60" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="F10" s="61" t="s">
         <v>240</v>
-      </c>
-      <c r="D9" s="58" t="s">
-        <v>241</v>
-      </c>
-      <c r="E9" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="F9" s="59" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="B10" s="61" t="s">
-        <v>245</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>246</v>
-      </c>
-      <c r="D10" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="E10" s="61" t="s">
-        <v>248</v>
-      </c>
-      <c r="F10" s="62" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3888,290 +3829,290 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="39.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="45.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.97"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="69" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="70" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="70" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="E3" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>247</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="57" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="70" t="s">
+      <c r="E4" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-    </row>
-    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="71" t="s">
+      <c r="F4" s="57" t="s">
         <v>252</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="G4" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="D3" s="71" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="60" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="C5" s="61" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="60" t="s">
         <v>255</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="E5" s="60" t="s">
         <v>256</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="F5" s="60" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="58" t="s">
+      <c r="G5" s="33" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>258</v>
       </c>
-      <c r="C4" s="59" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="58" t="s">
+      <c r="C6" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="57" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E6" s="57" t="s">
         <v>260</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F6" s="57" t="s">
         <v>261</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G6" s="32" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="61" t="s">
+    <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="60" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="62" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="61" t="s">
+      <c r="C7" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="60" t="s">
         <v>264</v>
       </c>
-      <c r="E5" s="61" t="s">
+      <c r="E7" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="F5" s="61" t="s">
+      <c r="F7" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G7" s="33" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="58" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>267</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>270</v>
+      </c>
+      <c r="G8" s="32" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="58" t="s">
-        <v>267</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>268</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="58" t="s">
-        <v>270</v>
-      </c>
-      <c r="G6" s="32" t="s">
+    <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="61" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="60" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="62" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="61" t="s">
+      <c r="C9" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="C7" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="61" t="s">
+      <c r="E9" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="E7" s="61" t="s">
+      <c r="F9" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="G9" s="33" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="58" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="57" t="s">
         <v>275</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="C10" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>277</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>282</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="F11" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="58" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>288</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="59" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="59" t="s">
+    <row r="13" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="58" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>278</v>
-      </c>
-      <c r="F8" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>281</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>282</v>
-      </c>
-      <c r="F9" s="61" t="s">
-        <v>283</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="59" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="58" t="s">
-        <v>284</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="E10" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="F10" s="58" t="s">
-        <v>287</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="61" t="s">
-        <v>289</v>
-      </c>
-      <c r="C11" s="62" t="s">
+      <c r="D13" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="D11" s="61" t="s">
+      <c r="E13" s="60" t="s">
         <v>291</v>
       </c>
-      <c r="E11" s="61" t="s">
+      <c r="F13" s="60" t="s">
         <v>292</v>
       </c>
-      <c r="F11" s="61" t="s">
-        <v>293</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="59" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>294</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>295</v>
-      </c>
-      <c r="E12" s="58" t="s">
-        <v>296</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>297</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="62" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="61" t="s">
-        <v>298</v>
-      </c>
-      <c r="C13" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="61" t="s">
-        <v>299</v>
-      </c>
-      <c r="E13" s="61" t="s">
-        <v>300</v>
-      </c>
-      <c r="F13" s="61" t="s">
-        <v>301</v>
-      </c>
       <c r="G13" s="33" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -4195,314 +4136,314 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="56" t="s">
-        <v>302</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
+      <c r="A1" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
+        <v>294</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="71" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="72" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="60" t="s">
         <v>303</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="C4" s="60" t="s">
+        <v>300</v>
+      </c>
+      <c r="D4" s="60" t="s">
         <v>304</v>
       </c>
-      <c r="C2" s="41" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="s">
         <v>305</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="B5" s="57" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="72" t="s">
+      <c r="C5" s="57" t="s">
         <v>307</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="D5" s="57" t="s">
         <v>308</v>
       </c>
-      <c r="C3" s="58" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="72" t="s">
         <v>309</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="B6" s="60" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="73" t="s">
+      <c r="C6" s="60" t="s">
         <v>311</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="D6" s="60" t="s">
         <v>312</v>
       </c>
-      <c r="C4" s="61" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="61" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="71" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="72" t="s">
+      <c r="B7" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="C7" s="57" t="s">
         <v>315</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="D7" s="57" t="s">
         <v>316</v>
       </c>
-      <c r="D5" s="58" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="72" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="73" t="s">
+      <c r="B8" s="60" t="s">
         <v>318</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="C8" s="60" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="60" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="61" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="71" t="s">
         <v>320</v>
       </c>
-      <c r="D6" s="61" t="s">
+      <c r="B9" s="57" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="72" t="s">
+      <c r="C9" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="57" t="s">
         <v>322</v>
       </c>
-      <c r="B7" s="58" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="72" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="60" t="s">
         <v>323</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C10" s="60" t="s">
+        <v>307</v>
+      </c>
+      <c r="D10" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="D7" s="58" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="71" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73" t="s">
+      <c r="B11" s="57" t="s">
         <v>326</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="C11" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="C8" s="61" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="61" t="s">
+      <c r="D11" s="57" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="72" t="s">
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="72" t="s">
         <v>329</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B12" s="60" t="s">
         <v>330</v>
       </c>
-      <c r="C9" s="58" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="58" t="s">
+      <c r="C12" s="60" t="s">
+        <v>300</v>
+      </c>
+      <c r="D12" s="60" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="61" t="s">
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="71" t="s">
         <v>332</v>
       </c>
-      <c r="C10" s="61" t="s">
-        <v>316</v>
-      </c>
-      <c r="D10" s="61" t="s">
+      <c r="B13" s="57" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="72" t="s">
+      <c r="C13" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" s="57" t="s">
         <v>334</v>
       </c>
-      <c r="B11" s="58" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="72" t="s">
         <v>335</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="B14" s="60" t="s">
         <v>336</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="C14" s="60" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="73" t="s">
+      <c r="D14" s="60" t="s">
         <v>338</v>
       </c>
-      <c r="B12" s="61" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="71" t="s">
         <v>339</v>
       </c>
-      <c r="C12" s="61" t="s">
-        <v>309</v>
-      </c>
-      <c r="D12" s="61" t="s">
+      <c r="B15" s="57" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="72" t="s">
+      <c r="C15" s="57" t="s">
         <v>341</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="D15" s="57" t="s">
         <v>342</v>
       </c>
-      <c r="C13" s="58" t="s">
-        <v>238</v>
-      </c>
-      <c r="D13" s="58" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="60" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="73" t="s">
+      <c r="C16" s="60" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="60" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="61" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" s="57" t="s">
         <v>345</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C17" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17" s="57" t="s">
         <v>346</v>
       </c>
-      <c r="D14" s="61" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="72" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="72" t="s">
+      <c r="B18" s="60" t="s">
         <v>348</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="C18" s="60" t="s">
         <v>349</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="D18" s="60" t="s">
         <v>350</v>
       </c>
-      <c r="D15" s="58" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="71" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="73" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" s="61" t="s">
+      <c r="B19" s="57" t="s">
         <v>352</v>
       </c>
-      <c r="C16" s="61" t="s">
-        <v>238</v>
-      </c>
-      <c r="D16" s="61" t="s">
+      <c r="C19" s="57" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="72" t="s">
-        <v>148</v>
-      </c>
-      <c r="B17" s="58" t="s">
+      <c r="D19" s="57" t="s">
         <v>354</v>
       </c>
-      <c r="C17" s="58" t="s">
-        <v>238</v>
-      </c>
-      <c r="D17" s="58" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="72" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="73" t="s">
+      <c r="B20" s="60" t="s">
         <v>356</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="C20" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="D20" s="60" t="s">
         <v>357</v>
       </c>
-      <c r="C18" s="61" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="57" t="s">
         <v>358</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="C21" s="57" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" s="57" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="s">
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="72" t="s">
         <v>360</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B22" s="60" t="s">
         <v>361</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C22" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="60" t="s">
         <v>362</v>
-      </c>
-      <c r="D19" s="58" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="73" t="s">
-        <v>364</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>365</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>350</v>
-      </c>
-      <c r="D20" s="61" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="72" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" s="58" t="s">
-        <v>367</v>
-      </c>
-      <c r="C21" s="58" t="s">
-        <v>358</v>
-      </c>
-      <c r="D21" s="58" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="73" t="s">
-        <v>369</v>
-      </c>
-      <c r="B22" s="61" t="s">
-        <v>370</v>
-      </c>
-      <c r="C22" s="61" t="s">
-        <v>214</v>
-      </c>
-      <c r="D22" s="61" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
